--- a/data/trans_dic/PCS12_SP_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/PCS12_SP_R2-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12)</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>39,19; 46,13</t>
+          <t>39,11; 46,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41,23; 49,2</t>
+          <t>41,48; 49,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39,33; 47,19</t>
+          <t>39,33; 46,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45,89; 55,12</t>
+          <t>46,61; 55,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>53,54; 61,08</t>
+          <t>53,65; 61,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,69; 57,08</t>
+          <t>49,31; 57,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,43; 55,12</t>
+          <t>47,39; 55,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>51,43; 57,57</t>
+          <t>51,31; 57,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>47,11; 52,53</t>
+          <t>47,35; 52,5</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46,53; 52,19</t>
+          <t>46,59; 51,85</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44,48; 50,02</t>
+          <t>44,6; 50,04</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>49,86; 55,23</t>
+          <t>49,89; 55,49</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>36,49; 42,87</t>
+          <t>36,66; 43,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40,83; 47,3</t>
+          <t>40,96; 47,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,83; 39,98</t>
+          <t>33,83; 39,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35,55; 73,15</t>
+          <t>36,34; 74,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>57,3; 63,54</t>
+          <t>56,93; 63,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,22; 58,64</t>
+          <t>52,19; 58,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,9; 50,24</t>
+          <t>43,95; 50,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>47,49; 53,28</t>
+          <t>47,72; 53,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>47,73; 52,33</t>
+          <t>47,66; 52,34</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47,3; 51,91</t>
+          <t>47,31; 51,74</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39,63; 44,17</t>
+          <t>39,66; 44,06</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>43,07; 65,62</t>
+          <t>43,26; 67,19</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>43,15; 50,49</t>
+          <t>42,79; 50,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37,23; 44,86</t>
+          <t>37,03; 44,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,72; 44,19</t>
+          <t>36,57; 44,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40,56; 48,8</t>
+          <t>40,64; 49,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>53,36; 60,94</t>
+          <t>53,06; 60,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>48,95; 56,45</t>
+          <t>49,03; 56,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,55; 52,6</t>
+          <t>45,33; 52,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>48,45; 79,4</t>
+          <t>48,37; 79,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49,2; 54,67</t>
+          <t>49,03; 54,31</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44,05; 49,37</t>
+          <t>44,28; 49,51</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42,28; 47,31</t>
+          <t>42,43; 47,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>45,92; 70,09</t>
+          <t>46,21; 70,94</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,38; 45,31</t>
+          <t>39,29; 45,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41,89; 48,63</t>
+          <t>42,01; 48,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,76; 40,0</t>
+          <t>33,68; 40,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48,86; 55,97</t>
+          <t>48,95; 56,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,74; 57,2</t>
+          <t>50,93; 57,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,12; 58,24</t>
+          <t>51,94; 58,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,28; 48,59</t>
+          <t>42,46; 48,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>43,47; 57,84</t>
+          <t>42,51; 57,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>46,18; 50,67</t>
+          <t>46,53; 50,85</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48,05; 52,75</t>
+          <t>48,09; 52,71</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39,38; 43,8</t>
+          <t>39,3; 43,64</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>46,65; 56,07</t>
+          <t>46,56; 55,89</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>40,98; 44,5</t>
+          <t>40,73; 44,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>42,18; 45,89</t>
+          <t>42,44; 45,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37,42; 40,7</t>
+          <t>37,29; 40,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45,22; 61,45</t>
+          <t>45,41; 60,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>55,36; 58,85</t>
+          <t>55,21; 58,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,61; 56,21</t>
+          <t>52,67; 56,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,97; 49,62</t>
+          <t>46,23; 49,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>50,93; 63,17</t>
+          <t>50,94; 63,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>48,6; 51,16</t>
+          <t>48,72; 51,17</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48,01; 50,45</t>
+          <t>47,99; 50,47</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42,23; 44,64</t>
+          <t>42,19; 44,71</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>49,01; 58,43</t>
+          <t>49,02; 58,99</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12)</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>272014; 320175</t>
+          <t>271425; 322551</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>290021; 346088</t>
+          <t>291826; 345438</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>265392; 318431</t>
+          <t>265392; 315169</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>289181; 347332</t>
+          <t>293691; 350289</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>368559; 420439</t>
+          <t>369301; 419918</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>346334; 397869</t>
+          <t>343694; 399080</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>319101; 370863</t>
+          <t>318876; 370403</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>344521; 385655</t>
+          <t>343725; 386736</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>651276; 726156</t>
+          <t>654559; 725744</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>651593; 730897</t>
+          <t>652481; 726191</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>599455; 674033</t>
+          <t>601100; 674318</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>648223; 717960</t>
+          <t>648622; 721432</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>350935; 412347</t>
+          <t>352567; 415782</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>415587; 481524</t>
+          <t>416935; 480001</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>345844; 408778</t>
+          <t>345939; 404936</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>422403; 869290</t>
+          <t>431867; 882277</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>554915; 615301</t>
+          <t>551349; 613157</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>539009; 605222</t>
+          <t>538650; 605340</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>457884; 523941</t>
+          <t>458383; 521511</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>452491; 507694</t>
+          <t>454658; 508104</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>921325; 1010021</t>
+          <t>919994; 1010277</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>969750; 1064219</t>
+          <t>969982; 1060796</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>818496; 912252</t>
+          <t>819016; 909925</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>922145; 1405031</t>
+          <t>926346; 1438564</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>292792; 342563</t>
+          <t>290342; 343622</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>282089; 339895</t>
+          <t>280581; 337897</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>278881; 335634</t>
+          <t>277765; 335397</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>284846; 342758</t>
+          <t>285413; 344891</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>364877; 416722</t>
+          <t>362846; 415527</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>380430; 438748</t>
+          <t>381069; 438409</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>357585; 412940</t>
+          <t>355864; 412866</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>451342; 739759</t>
+          <t>450603; 739663</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>670271; 744809</t>
+          <t>667935; 739873</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>676145; 757730</t>
+          <t>679672; 759925</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>652990; 730656</t>
+          <t>655432; 733420</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>750391; 1145161</t>
+          <t>755047; 1159167</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>371004; 426945</t>
+          <t>370172; 427258</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>397007; 460902</t>
+          <t>398169; 461560</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>316544; 375050</t>
+          <t>315738; 375840</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>450889; 516546</t>
+          <t>451739; 518039</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>527013; 594121</t>
+          <t>528927; 594130</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>548258; 612590</t>
+          <t>546318; 612409</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>441266; 507162</t>
+          <t>443212; 509929</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>473485; 630036</t>
+          <t>463002; 631214</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>914720; 1003645</t>
+          <t>921725; 1007201</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>960741; 1054730</t>
+          <t>961661; 1054079</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>780164; 867857</t>
+          <t>778602; 864645</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>938718; 1128301</t>
+          <t>936886; 1124632</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1342788; 1458215</t>
+          <t>1334686; 1458948</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1445255; 1572564</t>
+          <t>1454404; 1573064</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1270293; 1381491</t>
+          <t>1265887; 1383208</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1557120; 2116180</t>
+          <t>1563703; 2095632</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1870650; 1988583</t>
+          <t>1865497; 1982855</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1871924; 2000271</t>
+          <t>1874277; 1994639</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1629512; 1758713</t>
+          <t>1638475; 1758059</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1855580; 2301535</t>
+          <t>1855890; 2301980</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3234788; 3405160</t>
+          <t>3242413; 3406066</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3353430; 3524304</t>
+          <t>3351809; 3525395</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2930007; 3097352</t>
+          <t>2927561; 3102177</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3473685; 4140835</t>
+          <t>3474211; 4180808</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/PCS12_SP_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/PCS12_SP_R2-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,11%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>39,11; 46,48</t>
+          <t>39,13; 46,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41,48; 49,1</t>
+          <t>41,48; 49,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39,33; 46,71</t>
+          <t>39,22; 47,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46,61; 55,59</t>
+          <t>46,27; 54,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>53,65; 61,0</t>
+          <t>53,26; 61,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,31; 57,25</t>
+          <t>49,71; 57,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,39; 55,05</t>
+          <t>47,16; 55,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>51,31; 57,73</t>
+          <t>50,55; 56,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>47,35; 52,5</t>
+          <t>47,38; 52,83</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46,59; 51,85</t>
+          <t>46,65; 51,74</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44,6; 50,04</t>
+          <t>44,66; 50,04</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>49,89; 55,49</t>
+          <t>49,35; 54,41</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>43,46%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>36,66; 43,23</t>
+          <t>36,18; 42,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40,96; 47,15</t>
+          <t>40,96; 47,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,83; 39,61</t>
+          <t>33,85; 40,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36,34; 74,25</t>
+          <t>33,69; 40,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>56,93; 63,32</t>
+          <t>56,8; 63,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,19; 58,65</t>
+          <t>52,29; 58,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,95; 50,01</t>
+          <t>43,58; 49,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>47,72; 53,33</t>
+          <t>47,14; 52,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>47,66; 52,34</t>
+          <t>47,77; 52,29</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47,31; 51,74</t>
+          <t>47,2; 51,94</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39,66; 44,06</t>
+          <t>39,87; 44,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>43,26; 67,19</t>
+          <t>41,37; 45,44</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>48,59%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>42,79; 50,64</t>
+          <t>42,94; 50,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37,03; 44,6</t>
+          <t>37,03; 44,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,57; 44,16</t>
+          <t>36,7; 44,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40,64; 49,11</t>
+          <t>41,36; 49,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>53,06; 60,76</t>
+          <t>53,13; 60,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,03; 56,41</t>
+          <t>48,72; 56,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,33; 52,59</t>
+          <t>45,3; 52,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>48,37; 79,39</t>
+          <t>48,84; 55,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49,03; 54,31</t>
+          <t>48,94; 54,45</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44,28; 49,51</t>
+          <t>44,16; 49,54</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42,43; 47,48</t>
+          <t>42,31; 47,52</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>46,21; 70,94</t>
+          <t>46,04; 51,09</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,86%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,29; 45,35</t>
+          <t>39,52; 45,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42,01; 48,7</t>
+          <t>42,13; 48,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,68; 40,09</t>
+          <t>33,89; 40,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48,95; 56,13</t>
+          <t>48,01; 54,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,93; 57,2</t>
+          <t>50,95; 57,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,94; 58,22</t>
+          <t>52,07; 58,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,46; 48,85</t>
+          <t>42,48; 48,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>42,51; 57,95</t>
+          <t>53,57; 58,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>46,53; 50,85</t>
+          <t>46,09; 50,53</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48,09; 52,71</t>
+          <t>48,19; 52,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39,3; 43,64</t>
+          <t>39,26; 43,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>46,56; 55,89</t>
+          <t>51,82; 56,14</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>49,31%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>40,73; 44,53</t>
+          <t>40,72; 44,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>42,44; 45,91</t>
+          <t>42,17; 45,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37,29; 40,75</t>
+          <t>37,42; 40,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45,41; 60,85</t>
+          <t>43,74; 47,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>55,21; 58,68</t>
+          <t>55,26; 58,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,67; 56,06</t>
+          <t>52,73; 55,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,23; 49,6</t>
+          <t>46,06; 49,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>50,94; 63,18</t>
+          <t>51,61; 54,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>48,72; 51,17</t>
+          <t>48,72; 51,26</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47,99; 50,47</t>
+          <t>48,15; 50,48</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42,19; 44,71</t>
+          <t>42,2; 44,66</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>49,02; 58,99</t>
+          <t>48,13; 50,47</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>320510</t>
+          <t>346343</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>364395</t>
+          <t>389284</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>684904</t>
+          <t>735627</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>271425; 322551</t>
+          <t>271561; 323288</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>291826; 345438</t>
+          <t>291790; 344842</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>265392; 315169</t>
+          <t>264685; 317405</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>293691; 350289</t>
+          <t>316867; 374752</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>369301; 419918</t>
+          <t>366634; 421056</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>343694; 399080</t>
+          <t>346520; 398662</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>318876; 370403</t>
+          <t>317285; 370077</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>343725; 386736</t>
+          <t>367499; 411799</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>654559; 725744</t>
+          <t>654932; 730336</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>652481; 726191</t>
+          <t>653359; 724680</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>601100; 674318</t>
+          <t>601826; 674320</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>648622; 721432</t>
+          <t>696721; 768152</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>593664</t>
+          <t>384901</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>479906</t>
+          <t>531684</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1073570</t>
+          <t>916586</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>352567; 415782</t>
+          <t>348017; 411343</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>416935; 480001</t>
+          <t>416993; 482445</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>345939; 404936</t>
+          <t>346064; 409876</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>431867; 882277</t>
+          <t>351628; 420143</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>551349; 613157</t>
+          <t>550050; 611712</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>538650; 605340</t>
+          <t>539747; 604571</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>458383; 521511</t>
+          <t>454502; 519751</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>454658; 508104</t>
+          <t>502130; 562040</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>919994; 1010277</t>
+          <t>922126; 1009392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>969982; 1060796</t>
+          <t>967673; 1064915</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>819016; 909925</t>
+          <t>823455; 914763</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>926346; 1438564</t>
+          <t>872451; 958388</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>314566</t>
+          <t>362673</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>568177</t>
+          <t>420058</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>882743</t>
+          <t>782731</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>290342; 343622</t>
+          <t>291319; 342150</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>280581; 337897</t>
+          <t>280512; 340049</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>277765; 335397</t>
+          <t>278753; 337328</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>285413; 344891</t>
+          <t>330994; 394367</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>362846; 415527</t>
+          <t>363353; 411789</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>381069; 438409</t>
+          <t>378638; 438782</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>355864; 412866</t>
+          <t>355583; 414009</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>450603; 739663</t>
+          <t>395813; 447987</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>667935; 739873</t>
+          <t>666670; 741818</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>679672; 759925</t>
+          <t>677698; 760294</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>655432; 733420</t>
+          <t>653511; 734039</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>755047; 1159167</t>
+          <t>741655; 822860</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>486171</t>
+          <t>504639</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>581314</t>
+          <t>625950</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1067485</t>
+          <t>1130589</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>370172; 427258</t>
+          <t>372373; 430526</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>398169; 461560</t>
+          <t>399286; 463299</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>315738; 375840</t>
+          <t>317739; 377263</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>451739; 518039</t>
+          <t>473434; 536326</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>528927; 594130</t>
+          <t>529206; 592843</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>546318; 612409</t>
+          <t>547740; 613933</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>443212; 509929</t>
+          <t>443368; 508293</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>463002; 631214</t>
+          <t>596283; 654925</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>921725; 1007201</t>
+          <t>913018; 1000938</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>961661; 1054079</t>
+          <t>963719; 1057283</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>778602; 864645</t>
+          <t>777880; 864870</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>936886; 1124632</t>
+          <t>1087743; 1178599</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1714911</t>
+          <t>1598557</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1993792</t>
+          <t>1966976</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3708703</t>
+          <t>3565533</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1334686; 1458948</t>
+          <t>1334087; 1455877</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1454404; 1573064</t>
+          <t>1445018; 1567650</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1265887; 1383208</t>
+          <t>1270190; 1384774</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1563703; 2095632</t>
+          <t>1537537; 1660921</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1865497; 1982855</t>
+          <t>1867507; 1984856</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1874277; 1994639</t>
+          <t>1876130; 1990743</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1638475; 1758059</t>
+          <t>1632684; 1752258</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1855890; 2301980</t>
+          <t>1917711; 2026014</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3242413; 3406066</t>
+          <t>3242541; 3411872</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3351809; 3525395</t>
+          <t>3363111; 3526124</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2927561; 3102177</t>
+          <t>2928023; 3099135</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3474211; 4180808</t>
+          <t>3480317; 3649031</t>
         </is>
       </c>
     </row>
